--- a/data_extactor/batch_10_fa/batch_0083_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0083_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | استراتژی‌های یادگیری | یادگیری فعال | گوش دادن فعال | سخن‌گفتن | درک مطلب خواندنی</t>
+          <t>تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | خدمات مشتریان و پرسنل | طراحی | حمل‌ونقل | مهندسی و فناوری | ریاضیات | مکانیک | قانون و حکومت | زبان انگلیسی | آموزش و پرورش | تولید و فرآوری</t>
+          <t>ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | طراحی | حمل و نقل | مهندسی و فناوری | ریاضیات | مکانیک | قانون و دولت | زبان انگلیسی | آموزش و پرورش | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>هماهنگی چند عضو | دقت کنترل | ثبات دست و بازو | چالاکی دستی | چالاکی انگشتان | زمان عکس‌العمل | حساسیت به مسئله | تجسم فضایی | قدرت تنه | بینایی نزدیک | قدرت ایستا | انعطاف‌پذیری گسترده | درک عمق | درک شفاهی | جهت‌گیری پاسخ | استقامت | بینایی دور | تعادل کلی بدن | هماهنگی کلی بدن | تشخیص گفتار | تشخیص رنگ بصری | سرعت مچ و انگشت | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | توجه انتخابی | کنترل نرخ | روان بودن ایده‌ها | وضوح گفتار | انعطاف‌پذیری بستار | جهت‌گیری فضایی | سرعت ادراکی | استدلال استقرایی | سرعت حرکت اعضا | اصالت | اشتراک زمانی | بیان کتبی | درک کتبی | توجه شنیداری | حساسیت شنوایی | قدرت پویا</t>
+          <t>هماهنگی چند عضو | دقت کنترل | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | زمان عکس‌العمل | حساسیت به مسئله | تجسم | قدرت تنه | بینایی نزدیک | قدرت ایستا | انعطاف‌پذیری دامنه حرکت | درک عمق | درک شفاهی | جهت‌گیری پاسخ | استقامت | بینایی دور | تعادل کلی بدن | هماهنگی کلی بدن | تشخیص گفتار | تشخیص رنگ بصری | سرعت مچ و انگشتان | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | توجه انتخابی | کنترل نرخ | روانی ایده‌ها | وضوح گفتار | انعطاف‌پذیری بستار | جهت‌گیری فضایی | سرعت ادراکی | استدلال استقرایی | سرعت حرکت اعضا | اصالت | تقسیم توجه | بیان کتبی | درک کتبی | توجه شنیداری | حساسیت شنوایی | قدرت پویا</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان به حالت ایستاده | صرف زمان برای خم شدن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | فراوانی تصمیم‌گیری | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | قرار گرفتن در معرض دمای بسیار گرم یا سرد | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | پیامدهای کاری و نتایج سایر کارگران | نزدیکی فیزیکی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | موقعیت‌های تعارض | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها</t>
+          <t>قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای ایستادن | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | موقعیت‌های تعارض | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نجاران | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل‌ونقل | برقی‌کاران | مونتاژکنندگان موتور و سایر ماشین‌آلات | دستیاران--بناهای آجر، بناهای بلوک، سنگ‌تراشان و نصابان کاشی و مرمر | دستیاران--برقی‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | مکانیک‌های ماشین‌آلات صنعتی | کارگران طرح‌ریزی، فلز و پلاستیک | کارگران نگهداری و تعمیرات، عمومی | سازندگان آسیاب صنعتی | مکانیک‌های تجهیزات سنگین سیار، به جز موتورها | مدل‌سازان، چوب | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران آهن و فولاد سازه‌ای | سازندگان و مونتاژکنندگان فلزات سازه‌ای</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نجّاران | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | برق‌کاران | مونتاژکاران موتور و سایر ماشین‌آلات | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--برق‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | مکانیک‌های ماشین‌آلات صنعتی | کارگران شابلون‌زنی، فلز و پلاستیک | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مدل‌سازان چوب | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب خواندنی | گوش دادن فعال | تفکر انتقادی | مانیتورینگ | سخن‌گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | تولید و فرآوری | خدمات مشتریان و پرسنل | مدیریت و سازماندهی | طراحی | زبان انگلیسی | آموزش و پرورش | مهندسی و فناوری | ساختمان و ساخت‌وساز | ریاضیات</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | تولید و فرآوری | خدمات مشتری و شخصی | مدیریت و اداره | طراحی | زبان انگلیسی | آموزش و پرورش | مهندسی و فناوری | ساختمان و ساخت‌وساز | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک عمق | بینایی نزدیک | هماهنگی چند عضو | دقت کنترل | درک شفاهی | ترتیب‌دهی اطلاعات | قدرت تنه | بینایی دور | تشخیص گفتار | انعطاف‌پذیری گسترده | قدرت ایستا | زمان عکس‌العمل | چالاکی دستی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | وضوح گفتار | توجه شنیداری | تعادل کلی بدن | هماهنگی کلی بدن | چالاکی انگشتان | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی</t>
+          <t>حساسیت به مسئله | درک عمق | بینایی نزدیک | هماهنگی چند عضو | دقت کنترل | درک شفاهی | ترتیب‌دهی اطلاعات | قدرت تنه | بینایی دور | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | زمان عکس‌العمل | مهارت دستی | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | وضوح گفتار | توجه شنیداری | تعادل کلی بدن | هماهنگی کلی بدن | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض دمای بسیار گرم یا سرد | فشار زمانی | ارتباط با دیگران | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | قرار گرفتن در معرض تجهیزات خطرناک | فضای بسته، بدون کنترل شرایط محیطی | مکالمات تلفنی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان به حالت ایستاده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | پیامد خطا | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | صرف زمان برای خم شدن یا چرخاندن بدن | سرعت تعیین‌شده توسط سرعت تجهیزات | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا نامناسب | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | ارتباط با دیگران | فضای باز، در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض تجهیزات خطرناک | محیط داخلی، بدون کنترل شرایط محیطی | مکالمات تلفنی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | پیامد خطا | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان برای خم کردن یا چرخاندن بدن | سرعت تعیین‌شده توسط سرعت تجهیزات | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | اپراتورهای جرثقیل و برج | نصابان و تعمیرکاران خطوط انتقال نیروی برق | اپراتورهای ماشین‌آلات حفاری، بارگیری و دراگ‌لاین، معدن‌کاری سطحی | دستیاران--برقی‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون‌های صنعتی | کارگران نگهداری، ماشین‌آلات | سازندگان آسیاب صنعتی | مکانیک‌های تجهیزات سنگین سیار، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساخت‌وساز | اپراتورهای شمع‌کوب | کارگران ساده، نفت و گاز | کارگران آهن و فولاد سازه‌ای | سازندگان و مونتاژکنندگان فلزات سازه‌ای | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات جوشکاری، لحیم‌کاری سخت و نرم | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | اپراتورهای جرثقیل و تاور | نصابان و تعمیرکاران خطوط انتقال نیروی برق | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | دستیاران--برق‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | کارگران فنی همه‌کاره نفت و گاز | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Maintenance management software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Supervisory control and data acquisition SCADA software | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | مخابرات | مهندسی و فناوری | کامپیوتر و الکترونیک</t>
+          <t>حمل و نقل | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | مخابرات | مهندسی و فناوری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری بستار | تجسم فضایی | چالاکی دستی | چالاکی انگشتان | تشخیص رنگ بصری | بینایی دور | هماهنگی چند عضو | استدلال قیاسی | استدلال استقرایی | زمان عکس‌العمل | بینایی نزدیک | سرعت ادراکی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | درک عمق | قدرت تنه | توجه انتخابی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی</t>
+          <t>حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری بستار | تجسم | مهارت دستی | مهارت انگشتان | تشخیص رنگ بصری | بینایی دور | هماهنگی چند عضو | استدلال قیاسی | استدلال استقرایی | زمان عکس‌العمل | بینایی نزدیک | سرعت ادراکی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | درک عمق | قدرت تنه | توجه انتخابی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | قرار گرفتن در معرض دمای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به حالت ایستاده | قرار گرفتن در معرض تجهیزات خطرناک | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | قرار گرفتن در معرض تجهیزات خطرناک | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های اویونیک | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی برق | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | برقی‌کاران | تکنسین‌های روشنایی | مهندسان لوکوموتیو | مکانیک‌های تجهیزات سنگین سیار، به جز موتورها | توزیع‌کنندگان و دیسپچرهای برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل | تعمیرکاران واگن‌های ریلی | اپراتورهای ترمز، سیگنال و سوزن راه‌آهن و آتش‌کاران لوکوموتیو | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران خطوط مخابراتی</t>
+          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی برق | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | برق‌کاران | تکنسین‌های نورپردازی | مهندسان لوکوموتیو | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | توزیع‌کنندگان و دیسپچرهای برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | تعمیرکنندگان واگن‌های ریلی | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | مانیتورینگ | سخن‌گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتریان و پرسنل | ایمنی و امنیت عمومی | زبان انگلیسی | مهندسی و فناوری | ریاضیات | طراحی | تولید و فرآوری | کامپیوتر و الکترونیک</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | مهندسی و فناوری | ریاضیات | طراحی | تولید و فرآوری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چالاکی دستی | ثبات دست و بازو | بینایی نزدیک | دقت کنترل | هماهنگی چند عضو | چالاکی انگشتان | انعطاف‌پذیری گسترده | قدرت تنه | قدرت ایستا | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک شفاهی | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری بستار | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | استقامت</t>
+          <t>مهارت دستی | ثبات دست و بازو | بینایی نزدیک | دقت کنترل | هماهنگی چند عضو | مهارت انگشتان | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک شفاهی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | استقامت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فضای بسته، بدون کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | قرار گرفتن در معرض آلاینده‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | صرف زمان به حالت ایستاده | فراوانی تصمیم‌گیری | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | سلامت و ایمنی سایر کارگران | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دمای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامد خطا | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارگران</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، بدون کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامد خطا | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | دستیاران--بناهای آجر، بناهای بلوک، سنگ‌تراشان و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--برقی‌کاران | دستیاران--کارگران استخراج | دستیاران--نقاشان، کاغذدیوارکن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | دستیاران--کارگران تولید | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری، ماشین‌آلات | کارگران نگهداری و تعمیرات، عمومی | سازندگان آسیاب صنعتی | مکانیک‌های تجهیزات سنگین سیار، به جز موتورها | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات جوشکاری، لحیم‌کاری سخت و نرم</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کمک‌کاران--کارگران تولید | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم کامپیوتری مدیریت تعمیر و نگهداری CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب خواندنی | تفکر انتقادی | مانیتورینگ | گوش دادن فعال | سخن‌گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و ساخت‌وساز | کامپیوتر و الکترونیک | زبان انگلیسی | مهندسی و فناوری | خدمات مشتریان و پرسنل | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | رایانه و الکترونیک | زبان انگلیسی | مهندسی و فناوری | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم فضایی | ثبات دست و بازو | چالاکی انگشتان | چالاکی دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | صرف زمان به حالت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دمای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم شدن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارگران | نزدیکی فیزیکی | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | ارتباط با دیگران | فشار زمانی</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | ارتباط با دیگران | فشار زمانی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارگران نگهداری و تعمیرات، عمومی | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری، ماشین‌آلات | سازندگان آسیاب صنعتی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | نصابان سیستم‌های امنیتی و اعلام حریق | تعمیرکاران لوازم خانگی | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و تفریحی | قفل‌سازان و تعمیرکاران گاوصندوق | تعمیرکاران درب‌های مکانیکی | نصاب ساختمان‌های پیش‌ساخته و خانه‌های سیار | تکنسین‌های خدمات توربین بادی | تکنسین‌های زمین‌گرمایی | ریگرها | دستیاران--کارگران نصب، نگهداری و تعمیرات | سرپرستان رده اول مکانیک‌ها، نصابان و تعمیرکاران | برقی‌کاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | مدیران تاسیسات</t>
+          <t>کارگران نگهداری و تعمیرات عمومی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان نصب ماشین‌آلات | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | تعمیرکاران لوازم خانگی | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | قفل‌سازان و تعمیرکاران گاوصندوق | تعمیرکاران درب‌های مکانیکی | نصاب ساختمان‌های پیش‌ساخته و خانه‌های سیار | تکنسین‌های خدمات توربین بادی | تکنسین‌های زمین‌گرمایی | ریگرها | دستیاران--کارگران نصب، نگهداری و تعمیرات | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | برق‌کاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | مدیران تسهیلات</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | ClimateMaster GeoDesigner | سیستم کنترل توزیع‌شده DCS | نرم‌افزار ایمیل | سیستم‌های اطلاعات جغرافیایی GIS | ابزار اندازه‌گیری خواص زمین‌گرمایی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار SAP | Thermal Dynamics Ground Loop Design GLD | WaterFurnace International Ground Loop Design PREMIER</t>
+          <t>Autodesk AutoCAD | ClimateMaster GeoDesigner | سیستم کنترل توزیع‌شده DCS | نرم‌افزار ایمیل | سیستم‌های سیستم اطلاعات جغرافیایی GIS | ابزار اندازه‌گیری خواص زمین‌گرمایی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار SAP | Thermal Dynamics Ground Loop Design GLD | WaterFurnace International Ground Loop Design PREMIER</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>مانیتورینگ | درک مطلب خواندنی | تفکر انتقادی | یادگیری فعال | سخن‌گفتن | نگارش | گوش دادن فعال</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | سخن گفتن | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | فیزیک | آموزش و پرورش | ایمنی و امنیت عمومی | شیمی | مخابرات | طراحی | ریاضیات | تولید و فرآوری | مدیریت و سازماندهی | کامپیوتر و الکترونیک | اداری | مهندسی و فناوری</t>
+          <t>مکانیک | زبان انگلیسی | فیزیک | آموزش و پرورش | ایمنی و امنیت عمومی | شیمی | مخابرات | طراحی | ریاضیات | تولید و فرآوری | مدیریت و اداره | رایانه و الکترونیک | اداری | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | سرعت ادراکی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | تجسم فضایی | توجه انتخابی | دقت کنترل | تشخیص گفتار | تشخیص رنگ بصری | انعطاف‌پذیری گسترده | هماهنگی چند عضو | استدلال استقرایی | بیان کتبی | بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بینایی دور | قدرت تنه | زمان عکس‌العمل | چالاکی انگشتان | چالاکی دستی | اشتراک زمانی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | سرعت ادراکی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | تجسم | توجه انتخابی | دقت کنترل | تشخیص گفتار | تشخیص رنگ بصری | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | استدلال استقرایی | بیان کتبی | بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بینایی دور | قدرت تنه | زمان عکس‌العمل | مهارت انگشتان | مهارت دستی | تقسیم توجه | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | ایمیل | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارگران | فراوانی تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض دمای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | آزادی در تصمیم‌گیری | فضای بسته، بدون کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامد خطا | فضای بسته، با کنترل شرایط محیطی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت دقیق یا درست بودن | فشار زمانی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا نامناسب</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | قرار گرفتن در معرض شرایط خطرناک | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | ایمیل | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامد خطا | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت دقیق یا درست بودن | فشار زمانی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه زیست‌توده | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای تاسیسات گاز | مدیران تولید زمین‌گرمایی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مهندسان مکانیک | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه | نصابان سیستم‌های فتوولتائیک خورشیدی | نصابان و تکنسین‌های سیستم‌های حرارتی خورشیدی | مهندسان تاسیسات ثابت و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌زن‌های سر چاه | تکنسین‌های خدمات توربین بادی</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | مهندسان مکانیک | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | نصابان سیستم‌های فتوولتائیک خورشیدی | نصابان و تکنسین‌های حرارتی خورشیدی | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apple Safari | Apple iWork Pages | Aptean Made2Manage | Autodesk AutoCAD | Bowen &amp; Groves M1 ERP | Capterra Enterprise Resource Planning | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار ایمیل | Encompix ERP | Epicor Vantage ERP | Epicor Vista ERP | Exact MAX | Extensible markup language XML | GHG Clockwise | Giraffe Production Systems Giraffe Schedule System | Google Chrome | HCSS HeavyJob | IBM Notes | Intacct ERP | سیستم‌های یکپارچه مدیریت مواد | Kronos Workforce Timekeeper | نرم‌افزار مدیریت مواد | Microsoft Access | Microsoft Axapta | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Total Quality Control Management | Microsoft Word | Minitab | Mozilla Firefox | NetSuite NetERP | پایگاه‌های داده عملیاتی | Oracle JD Edwards EnterpriseOne | QA Software QMS Materials Management | نرم‌افزار برنامه‌ریزی منابع | Retain Resource Planning | SAP Business One | نرم‌افزار SAP | SYSPRO business software | Supervisory control and data acquisition SCADA software | Technology Group International Enterprise 21 ERP | نرم‌افزار ثبت زمان | نرم‌افزار مدیریت کیفیت جامع TQM | Work Technology WorkTech Time</t>
+          <t>Apple Safari | Apple iWork Pages | Aptean Made2Manage | Autodesk AutoCAD | Bowen &amp; Groves M1 ERP | Capterra Enterprise Resource Planning | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار ایمیل | Encompix ERP | Epicor Vantage ERP | Epicor Vista ERP | Exact MAX | زبان نشانه‌گذاری توسعه‌پذیر XML | GHG Clockwise | Giraffe Production Systems Giraffe Schedule System | Google Chrome | HCSS HeavyJob | IBM Notes | Intacct ERP | سیستم‌های یکپارچه مدیریت مواد | Kronos Workforce Timekeeper | Materials management software | Microsoft Access | Microsoft Axapta | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Total Quality Control Management | Microsoft Word | Minitab | Mozilla Firefox | NetSuite NetERP | پایگاه‌های داده عملیاتی | Oracle JD Edwards EnterpriseOne | QA Software QMS Materials Management | نرم‌افزار برنامه‌ریزی منابع | Retain Resource Planning | SAP Business One | نرم‌افزار SAP | SYSPRO business software | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Technology Group International Enterprise 21 ERP | نرم‌افزار ثبت زمان | نرم‌افزار TQM | Work Technology WorkTech Time</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن‌گفتن | تفکر انتقادی | مانیتورینگ | درک مطلب خواندنی | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و سازماندهی | پرسنل و منابع انسانی | زبان انگلیسی | کامپیوتر و الکترونیک | ریاضیات | اداری | مکانیک | آموزش و پرورش | مهندسی و فناوری</t>
+          <t>تولید و فرآوری | مدیریت و اداره | پرسنل و منابع انسانی | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | اداری | مکانیک | آموزش و پرورش | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تجسم فضایی | سرعت ادراکی | اصالت | روان بودن ایده‌ها | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی | بینایی دور | چالاکی دستی | ثبات دست و بازو</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تجسم | سرعت ادراکی | اصالت | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی | بینایی دور | مهارت دستی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | فراوانی تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | سلامت و ایمنی سایر کارگران | پیامدهای کاری و نتایج سایر کارگران | ایمیل | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فضای بسته، بدون کنترل شرایط محیطی | مکالمات تلفنی | صرف زمان به حالت ایستاده | سرعت تعیین‌شده توسط سرعت تجهیزات | موقعیت‌های تعارض | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دمای بسیار گرم یا سرد | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | فراوانی تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | ایمیل | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، بدون کنترل شرایط محیطی | مکالمات تلفنی | صرف زمان برای ایستادن | سرعت تعیین‌شده توسط سرعت تجهیزات | موقعیت‌های تعارض | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>سرپرستان رده اول مشاغل ساختمانی و استخراج | سرپرستان رده اول کارگران سرگرمی و تفریحی، به جز خدمات قمار | سرپرستان رده اول کارگران کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان رده اول کارگران تهیه و سرو غذا | سرپرستان رده اول دستیاران، کارگران ساده و جابجاکنندگان دستی مواد | سرپرستان رده اول کارگران خانه‌داری و سرایداری | سرپرستان رده اول کارگران محوطه‌سازی، خدمات چمن و نگهداری فضای سبز | سرپرستان رده اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان رده اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارگران فروش غیرخرده‌فروشی | سرپرستان رده اول کارگران پشتیبانی اداری و دفتری | سرپرستان رده اول مهمانداران مسافران | سرپرستان رده اول کارگران امنیتی | مدیران عمومی و عملیاتی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | کارمندان تولید، برنامه‌ریزی و هماهنگی | هماهنگ‌کنندگان بازیافت | مونتاژکنندگان تیمی</t>
+          <t>سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیات | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | کارمندان تولید، برنامه‌ریزی و هماهنگی | هماهنگ‌کنندگان بازیافت | مونتاژکاران تیمی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | مانیتورینگ | سخن‌گفتن | درک مطلب خواندنی</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ریاضیات | آموزش و پرورش | مکانیک | زبان انگلیسی | تولید و فرآوری | طراحی | کامپیوتر و الکترونیک | ایمنی و امنیت عمومی</t>
+          <t>ریاضیات | آموزش و پرورش | مکانیک | زبان انگلیسی | تولید و فرآوری | طراحی | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بینایی نزدیک | چالاکی انگشتان | چالاکی دستی | تجسم فضایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری گسترده | دقت کنترل | ثبات دست و بازو | استدلال قیاسی | درک کتبی | درک شفاهی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | توجه شنیداری | هماهنگی چند عضو | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | مهارت انگشتان | مهارت دستی | تجسم | ترتیب‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | دقت کنترل | ثبات دست و بازو | استدلال قیاسی | درک کتبی | درک شفاهی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | توجه شنیداری | هماهنگی چند عضو | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش, محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط خطرناک | فضای بسته، با کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به حالت ایستاده | اهمیت تکرار وظایف یکسان | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فشار زمانی</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط خطرناک | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فشار زمانی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های اویونیک | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | کارگران طرح‌ریزی، فلز و پلاستیک | ماشین‌کاران | کارگران نگهداری، ماشین‌آلات | کارگران نگهداری و تعمیرات، عمومی | سازندگان آسیاب صنعتی | مدل‌سازان، فلز و پلاستیک | کارگران ورق‌های فلزی | سازندگان و مونتاژکنندگان فلزات سازه‌ای | مونتاژکنندگان و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | جوشکاران، برش‌کاران، لحیم‌کاران سخت و نرم | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات جوشکاری، لحیم‌کاری سخت و نرم</t>
+          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های هوانوردی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | مدل‌سازان فلز و پلاستیک | کارگران ورق‌کاری | سازندگان و مونتاژکاران فلزات سازه‌ای | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | زبان انگلیسی | ریاضیات | مدیریت و سازماندهی | تولید و فرآوری | مکانیک | طراحی | کامپیوتر و الکترونیک</t>
+          <t>آموزش و پرورش | زبان انگلیسی | ریاضیات | مدیریت و اداره | تولید و فرآوری | مکانیک | طراحی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چالاکی دستی | دقت کنترل | بینایی نزدیک | چالاکی انگشتان | توجه انتخابی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
+          <t>ثبات دست و بازو | مهارت دستی | دقت کنترل | بینایی نزدیک | مهارت انگشتان | توجه انتخابی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | صرف زمان به حالت ایستاده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | پیامد خطا | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | فضای بسته، با کنترل شرایط محیطی | صرف زمان برای خم شدن یا چرخاندن بدن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات برش، پانچ و پرس، فلز و پلاستیک | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات اکستروژن و کشش، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات اکستروژن و شکل‌دهی، الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات آهنگری، فلز و پلاستیک | کارگران سنگ‌زنی و پولیش‌کاری، دستی | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌ابزارهای تراش و چرخ‌کاری، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات فرز و رنده، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌ابزارهای چندگانه، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات نورد، فلز و پلاستیک | مونتاژکنندگان و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | تیزکنندگان و سوهان‌کاران ابزار | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات جوشکاری، لحیم‌کاری سخت و نرم | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Calibration software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | National Instruments LabVIEW | Production control software | Rasmussen Software Anzio | نرم‌افزار SAP | Sage 100 ERP | Terminal emulation software</t>
+          <t>نرم‌افزار کالیبراسیون | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | National Instruments LabVIEW | Production control software | Rasmussen Software Anzio | نرم‌افزار SAP | Sage 100 ERP | نرم‌افزار شبیه‌سازی ترمینال</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب خواندنی | مانیتورینگ | تفکر انتقادی | گوش دادن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | کامپیوتر و الکترونیک | مکانیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | طراحی</t>
+          <t>تولید و فرآوری | رایانه و الکترونیک | مکانیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | طراحی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | چالاکی انگشتان | درک شفاهی | چالاکی دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | تجسم فضایی | استدلال استقرایی | بیان شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | تشخیص رنگ بصری | هماهنگی چند عضو | دقت کنترل</t>
+          <t>بینایی نزدیک | مهارت انگشتان | درک شفاهی | مهارت دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | تجسم | استدلال استقرایی | بیان شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | تشخیص رنگ بصری | هماهنگی چند عضو | دقت کنترل</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>فضای بسته، با کنترل شرایط محیطی | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | پیامدهای کاری و نتایج سایر کارگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | کارشناسان و تکنسین‌های کالیبراسیون | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران | مهندسان مکانیک | مدل‌سازان، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌ابزارهای چندگانه، فلز و پلاستیک | سازندگان و مونتاژکنندگان فلزات سازه‌ای | مونتاژکنندگان تیمی | مونتاژکنندگان و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | جوشکاران، برش‌کاران، لحیم‌کاران سخت و نرم | تنظیم‌کنندگان، اپراتورها و مسئولان ماشین‌آلات جوشکاری، لحیم‌کاری سخت و نرم</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران | مهندسان مکانیک | مدل‌سازان فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | سازندگان و مونتاژکاران فلزات سازه‌ای | مونتاژکاران تیمی | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0083_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0083_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | راهبردهای یادگیری | یادگیری فعال | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | طراحی | ترابری | مهندسی و فناوری | ریاضیات | مکانیک | حقوق و مقررات دولتی | زبان انگلیسی | آموزش و تدریس | تولید و فرآوری</t>
+          <t>ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | طراحی | حمل و نقل | مهندسی و فناوری | ریاضیات | مکانیک | قانون و دولت | زبان انگلیسی | آموزش و پرورش | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>هماهنگی چنداندام | دقت کنترل | ثبات دست و بازو | چابکی دستی | چابکی انگشتان | زمان واکنش | حساسیت به مسئله | تجسم فضایی | استحکام تنه | دید نزدیک | قدرت ایستا | انعطاف‌پذیری دامنه‌ای | درک عمق | درک شفاهی | جهت‌گیری پاسخ | استقامت بدنی | دید دور | تعادل کلی بدن | هماهنگی کلی بدن | تشخیص گفتار | تشخیص رنگ‌ها | سرعت مچ و انگشت | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی | بیان شفاهی | توجه انتخابی | کنترل نرخ حرکتی | روانی بیان ایده‌ها | وضوح گفتار | انعطاف بستار | جهت‌یابی فضایی | سرعت ادراک | استدلال استقرایی | سرعت حرکت اندام‌ها | ابتکار | اشتراک زمان | بیان کتبی | درک کتبی | توجه شنیداری | حساسیت شنوایی | قدرت پویا</t>
+          <t>هماهنگی چند عضو | دقت کنترل | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | زمان عکس‌العمل | حساسیت به مسئله | تجسم | قدرت تنه | بینایی نزدیک | قدرت ایستا | انعطاف‌پذیری دامنه حرکت | درک عمق | درک شفاهی | جهت‌گیری پاسخ | استقامت | بینایی دور | تعادل کلی بدن | هماهنگی کلی بدن | تشخیص گفتار | تشخیص رنگ بصری | سرعت مچ و انگشتان | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | توجه انتخابی | کنترل نرخ | روانی ایده‌ها | وضوح گفتار | انعطاف‌پذیری بستار | جهت‌گیری فضایی | سرعت ادراکی | استدلال استقرایی | سرعت حرکت اعضا | اصالت | تقسیم توجه | بیان کتبی | درک کتبی | توجه شنیداری | حساسیت شنوایی | قدرت پویا</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نجاران | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف کاذب | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | برق‌کاران | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران کمکی بنایی، بلوک‌چینی، سنگ‌کاری و کاشی‌کاری | کارگران کمکی برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | کارگران کمکی لوله‌کشی و اتصالات پایپینگ | مکانیک‌های ماشین‌آلات صنعتی | خط‌کشان و علامت‌گذاران فلز و پلاستیک | کارگران عمومی نگهداری و تعمیرات | نصابان و ترازکاران ماشین‌آلات سنگین (میل‌رایت) | مکانیک‌های تجهیزات سنگین متحرک (به‌جز موتور) | مدل‌سازان سازه‌های چوبی | لوله‌کشان و اتصالات‌کاران پایپینگ صنعتی | اسکلت‌سازان فلزی | سازندگان و مونتاژکاران قطعات فلزی سازه</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نجاران و درودگران | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | برق‌کاران | مونتاژکاران موتور و سایر ماشین‌آلات | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | مکانیک‌های ماشین‌آلات صنعتی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | مدل‌سازان چوب | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | تولید و فرآوری | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | طراحی | زبان انگلیسی | آموزش و تدریس | مهندسی و فناوری | ساختمان و سازه | ریاضیات</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | تولید و فرآوری | خدمات مشتری و شخصی | مدیریت و اداره | طراحی | زبان انگلیسی | آموزش و پرورش | مهندسی و فناوری | ساختمان و ساخت‌وساز | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک عمق | دید نزدیک | هماهنگی چنداندام | دقت کنترل | درک شفاهی | مرتب‌سازی اطلاعات | استحکام تنه | دید دور | تشخیص گفتار | انعطاف‌پذیری دامنه‌ای | قدرت ایستا | زمان واکنش | چابکی دستی | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | وضوح گفتار | توجه شنیداری | تعادل کلی بدن | هماهنگی کلی بدن | چابکی انگشتان | ثبات دست و بازو | توجه انتخابی | سرعت ادراک</t>
+          <t>حساسیت به مسئله | درک عمق | بینایی نزدیک | هماهنگی چند عضو | دقت کنترل | درک شفاهی | ترتیب‌دهی اطلاعات | قدرت تنه | بینایی دور | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | زمان عکس‌العمل | مهارت دستی | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | وضوح گفتار | توجه شنیداری | تعادل کلی بدن | هماهنگی کلی بدن | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | اپراتورهای جرثقیل و تاورکرین | نصابان و تعمیرکاران خطوط انتقال برق | اپراتورهای ماشین‌آلات حفاری و درگ‌لاین در معادن روباز | کارگران کمکی برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان لیفتراک و کشنده‌های صنعتی | کارگران نگهداری و سرویس ماشین‌آلات | نصابان و ترازکاران ماشین‌آلات سنگین (میل‌رایت) | مکانیک‌های تجهیزات سنگین متحرک (به‌جز موتور) | مکانیک‌ها و تکنسین‌های قایق‌های موتوری | اپراتورهای ماشین‌آلات عمرانی و مهندسی راه‌سازی | اپراتورهای شمع‌کوب | کارگران دکل و حفاری نفت و گاز (راستابات) | اسکلت‌سازان فلزی | سازندگان و مونتاژکاران قطعات فلزی سازه | تنظیم‌کنندگان و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات درودگری (به‌جز اره‌کشی)</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | اپراتورهای جرثقیل و تاورکرین | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کمک‌برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای دستگاه شمع‌کوب | کارگران عمومی سکو و میادین نفت و گاز | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ترابری | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | مخابرات | مهندسی و فناوری | رایانه و الکترونیک</t>
+          <t>حمل و نقل | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | مخابرات | مهندسی و فناوری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | انعطاف بستار | تجسم فضایی | چابکی دستی | چابکی انگشتان | تشخیص رنگ‌ها | دید دور | هماهنگی چنداندام | استدلال قیاسی | استدلال استقرایی | زمان واکنش | دید نزدیک | سرعت ادراک | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی | درک عمق | استحکام تنه | توجه انتخابی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی</t>
+          <t>حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری بستار | تجسم | مهارت دستی | مهارت انگشتان | تشخیص رنگ بصری | بینایی دور | هماهنگی چند عضو | استدلال قیاسی | استدلال استقرایی | زمان عکس‌العمل | بینایی نزدیک | سرعت ادراکی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | درک عمق | قدرت تنه | توجه انتخابی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های اویونیک و الکترونیک هوانوردی | مکانیک‌های اتوبوس، کامیون و موتورهای دیزلی | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | نصابان و تعمیرکاران خطوط انتقال برق | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکاران تجهیزات برقی و الکترونیکی تجاری و صنعتی | تعمیرکاران برق پست‌ها، نیروگاه‌ها و رله‌های حفاظتی | برق‌کاران | تکنسین‌های نور و روشنایی | لکوموتیورانان | مکانیک‌های تجهیزات سنگین متحرک (به‌جز موتور) | دیسپاچرها و توزیع‌کنندگان انرژی الکتریکی | نصابان و تعمیرکاران تجهیزات رادیویی، دکل‌ها و سایت‌های سلولار | تعمیرکاران واگن‌های قطار | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتش‌کاران لکوموتیو | نصابان و تعمیرکاران تجهیزات مخابراتی (به‌جز کابل‌کشی خطوط) | نصابان و تعمیرکاران خطوط کابل‌کشی مخابرات</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | برق‌کاران | تکنسین‌های نورپردازی | لکوموتیورانان | مکانیک تجهیزات سنگین متحرک | دیسپچرها و توزیع‌کنندگان شبکه برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | تعمیرکار واگن قطار | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | نصابان و کابل‌کشان خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و سازه | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | مهندسی و فناوری | ریاضیات | طراحی | تولید و فرآوری | رایانه و الکترونیک</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | مهندسی و فناوری | ریاضیات | طراحی | تولید و فرآوری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | دید نزدیک | دقت کنترل | هماهنگی چنداندام | چابکی انگشتان | انعطاف‌پذیری دامنه‌ای | استحکام تنه | قدرت ایستا | مرتب‌سازی اطلاعات | استدلال قیاسی | درک شفاهی | توجه انتخابی | تجسم فضایی | انعطاف بستار | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | استقامت بدنی</t>
+          <t>مهارت دستی | ثبات دست و بازو | بینایی نزدیک | دقت کنترل | هماهنگی چند عضو | مهارت انگشتان | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک شفاهی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | استقامت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان صنعتی (بویلرسازان) | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران کمکی بنایی، بلوک‌چینی، سنگ‌کاری و کاشی‌کاری | کارگران کمکی نجاران | کارگران کمکی برق‌کاران | کارگران کمکی استخراج معدن و چاه | کارگران کمکی نقاشان، کاغذدیواری‌کاران و گچ‌کاران | کارگران کمکی لوله‌کشی و اتصالات پایپینگ | کارگران کمکی خطوط تولید | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری و سرویس ماشین‌آلات | کارگران عمومی نگهداری و تعمیرات | نصابان و ترازکاران ماشین‌آلات سنگین (میل‌رایت) | مکانیک‌های تجهیزات سنگین متحرک (به‌جز موتور) | لوله‌کشان و اتصالات‌کاران پایپینگ صنعتی | تنظیم‌کنندگان و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌برق‌کاران | کارگران کمکی استخراج معدن | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کمک‌کارگران خطوط تولید | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و سازه | رایانه و الکترونیک | زبان انگلیسی | مهندسی و فناوری | خدمات مشتریان و خدمات فردی | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | رایانه و الکترونیک | زبان انگلیسی | مهندسی و فناوری | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دقت کنترل | هماهنگی چنداندام | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارگران عمومی نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری و سرویس ماشین‌آلات | نصابان و ترازکاران ماشین‌آلات سنگین (میل‌رایت) | مکانیک‌ها و نصابان سیستم‌های سرمایشی، گرمایشی و تهویه مطبوع | تعمیرکاران تجهیزات برقی و الکترونیکی تجاری و صنعتی | نصابان سیستم‌های اعلام و اطفای حریق و دزدگیر | تعمیرکاران لوازم خانگی | تعمیرکاران دستگاه‌های خودپرداز و تجهیزات سرگرمی سکه‌ای | قفل‌سازان و تعمیرکاران گاوصندوق | تعمیرکاران درب‌های اتوماتیک و کرکره‌های برقی | نصاب سازه‌های پیش‌ساخته و خانه‌های سیار | تکنسین‌های سرویس و نگهداری توربین بادی | تکنسین‌های سامانه‌های زمین‌گرمایی | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | کارگران کمکی نصب، نگهداری و تعمیرات | سرپرستان رده اول مکانیک‌ها، نصابان و تعمیرکاران | برق‌کاران | لوله‌کشان و اتصالات‌کاران پایپینگ صنعتی | مدیران تأسیسات</t>
+          <t>کارگران عمومی تعمیرات و نگهداری تاسیسات | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | نصاب سیستم‌های اعلام سرقت و حریق | تعمیرکاران لوازم خانگی | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | قفل‌سازان و تعمیرکاران گاوصندوق | تعمیرکاران درب‌های مکانیکی و اتوماتیک | نصاب سازه‌های پیش‌ساخته و خانه‌های سیار | تکنسین‌های تعمیر و نگهداری توربین‌های بادی | تکنسین‌های سامانه‌های زمین‌گرمایی | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | کارگران کمکی نصب، نگهداری و تعمیرات | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | برق‌کاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | مدیران امور ساختمان و تأسیسات</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | سخن گفتن | نگارش | شنیدن فعال</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | سخن گفتن | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | فیزیک | آموزش و تدریس | ایمنی و امنیت عمومی | شیمی | مخابرات | طراحی | ریاضیات | تولید و فرآوری | مدیریت و امور اداری | رایانه و الکترونیک | امور اداری و دفتری | مهندسی و فناوری</t>
+          <t>مکانیک | زبان انگلیسی | فیزیک | آموزش و پرورش | ایمنی و امنیت عمومی | شیمی | مخابرات | طراحی | ریاضیات | تولید و فرآوری | مدیریت و اداره | رایانه و الکترونیک | اداری | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | استدلال قیاسی | سرعت ادراک | ثبات دست و بازو | مرتب‌سازی اطلاعات | انعطاف بستار | تجسم فضایی | توجه انتخابی | دقت کنترل | تشخیص گفتار | تشخیص رنگ‌ها | انعطاف‌پذیری دامنه‌ای | هماهنگی چنداندام | استدلال استقرایی | بیان کتبی | بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | دید دور | استحکام تنه | زمان واکنش | چابکی انگشتان | چابکی دستی | اشتراک زمان | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | سرعت ادراکی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | تجسم | توجه انتخابی | دقت کنترل | تشخیص گفتار | تشخیص رنگ بصری | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | استدلال استقرایی | بیان کتبی | بیان شفاهی | درک شفاهی | درک کتبی | وضوح گفتار | بینایی دور | قدرت تنه | زمان عکس‌العمل | مهارت انگشتان | مهارت دستی | تقسیم توجه | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه‌های زیست‌توده (بیومس) | مدیران نیروگاه‌های زیست‌توده (بیومس) | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی | تعمیرکاران تجهیزات برقی و الکترونیکی تجاری و صنعتی | تعمیرکاران برق پست‌ها، نیروگاه‌ها و رله‌های حفاظتی | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | اپراتورهای پالایشگاه و تأسیسات گاز | مدیران تولید انرژی زمین‌گرمایی | مکانیک‌ها و نصابان سیستم‌های سرمایشی، گرمایشی و تهویه مطبوع | تکنسین‌های نیروگاه‌های برقابی | مدیران تولید نیروگاه‌های برقابی | مهندسان مکانیک | دیسپاچرها و توزیع‌کنندگان انرژی الکتریکی | اپراتورهای نیروگاه برق | نصابان سامانه‌های خورشیدی فتوولتائیک | نصابان و تکنسین‌های سامانه‌های خورشیدی حرارتی | تکنسین‌ها و اپراتورهای دیگ بخار و موتورخانه | اپراتورهای تصفیه‌خانه آب و فاضلاب صنعتی | پمپ‌رانان سرچاهی نفت و گاز | تکنسین‌های سرویس و نگهداری توربین بادی</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | مهندسان مکانیک | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | نصابان سیستم‌های خورشیدی فتوولتائیک | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپ سرچاهی نفت و گاز | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و امور اداری | امور اداری و منابع انسانی | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | امور اداری و دفتری | مکانیک | آموزش و تدریس | مهندسی و فناوری</t>
+          <t>تولید و فرآوری | مدیریت و اداره | پرسنل و منابع انسانی | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | اداری | مکانیک | آموزش و پرورش | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بیان کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | دید نزدیک | تجسم فضایی | سرعت ادراک | ابتکار | روانی بیان ایده‌ها | توجه انتخابی | انعطاف بستار | استدلال ریاضی | دید دور | چابکی دستی | ثبات دست و بازو</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تجسم | سرعت ادراکی | اصالت | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی | بینایی دور | مهارت دستی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>سرپرستان رده اول مشاغل ساختمانی و استخراج معدن | سرپرستان رده اول کارگران سرگرمی و تفریحی (به‌جز قمار) | سرپرستان رده اول کارگران کشاورزی، شیلات و جنگلداری | سرپرستان رده اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده اول کارگران کمکی و باربری دستی | سرپرستان رده اول خدمات عمومی، نظافت و خانه‌داری | سرپرستان رده اول فضای سبز و باغبانی | سرپرستان رده اول رانندگان ماشین‌آلات جابه‌جایی مواد | سرپرستان رده اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارشناسان فروش غیرخرده‌فروشی | سرپرستان رده اول کارکنان اداری و پشتیبانی | سرپرستان رده اول مهمانداران مسافری | سرپرستان رده اول نیروهای حراست و انتظامات | مدیران اجرایی و مدیران عملیات | تکنسین‌ها و کاردان‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان برنامه‌ریزی، کنترل تولید و پیگیری سفارش‌ها | کارشناسان هماهنگی بازیافت مواد | مونتاژکاران گروهی و خطوط تولید</t>
+          <t>سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیات | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | هماهنگ‌کنندگان امور بازیافت | مونتاژکاران گروهی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ریاضیات | آموزش و تدریس | مکانیک | زبان انگلیسی | تولید و فرآوری | طراحی | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
+          <t>ریاضیات | آموزش و پرورش | مکانیک | زبان انگلیسی | تولید و فرآوری | طراحی | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | چابکی انگشتان | چابکی دستی | تجسم فضایی | مرتب‌سازی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دامنه‌ای | دقت کنترل | ثبات دست و بازو | استدلال قیاسی | درک کتبی | درک شفاهی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | توجه شنیداری | هماهنگی چنداندام | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | مهارت انگشتان | مهارت دستی | تجسم | ترتیب‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | دقت کنترل | ثبات دست و بازو | استدلال قیاسی | درک کتبی | درک شفاهی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | توجه شنیداری | هماهنگی چند عضو | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مکانیک‌ها و تکنسین‌های خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک هوانوردی | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تکنسین‌ها و کاردان‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | خط‌کشان و علامت‌گذاران فلز و پلاستیک | ماشین‌کاران و تراشکاران | کارگران نگهداری و سرویس ماشین‌آلات | کارگران عمومی نگهداری و تعمیرات | نصابان و ترازکاران ماشین‌آلات سنگین (میل‌رایت) | مدل‌سازان صنعتی فلز و پلاستیک | کارشناسان ساخت و شکل‌دهی ورق‌های فلزی | سازندگان و مونتاژکاران قطعات فلزی سازه | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | جوشکاران، برشکاران و لحیم‌کاران | تنظیم‌کنندگان و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
+          <t>مکانیک و تکنسین خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مدل‌سازان فلز و پلاستیک | کارگران ورق‌کاری فلزی | سازندگان و مونتاژکاران سازه‌های فلزی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,22 +959,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار نمایش نقشه‌های فنی و بلوپرینت | Electronic Systems of Wisconsin Motor Test System | سامانه کنترل دستگاه بوبین‌پیچ Machine Control Specialists CoilPro</t>
+          <t>Blueprint display software | Electronic Systems of Wisconsin Motor Test System | سامانه کنترل دستگاه بوبین‌پیچ Machine Control Specialists CoilPro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | ریاضیات | مدیریت و امور اداری | تولید و فرآوری | مکانیک | طراحی | رایانه و الکترونیک</t>
+          <t>آموزش و پرورش | زبان انگلیسی | ریاضیات | مدیریت و اداره | تولید و فرآوری | مکانیک | طراحی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | دقت کنترل | دید نزدیک | چابکی انگشتان | توجه انتخابی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
+          <t>ثبات دست و بازو | مهارت دستی | دقت کنترل | بینایی نزدیک | مهارت انگشتان | توجه انتخابی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های پرس و برش‌کاری فلز و پلاستیک | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای اکستروژن الیاف شیشه و سنتزی | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | کارگران پرداخت‌کاری و سنباده‌زنی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌های سنگ‌زنی و پولیش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای دستگاه‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان خطوط تولید | تنظیم‌کنندگان و اپراتورهای دستگاه‌های فرزکاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندمنظوره | تنظیم‌کنندگان و اپراتورهای دستگاه‌های نورد فلز و پلاستیک | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | کارشناسان تیزکاری و سنگ‌زنی ابزارهای برشی | تنظیم‌کنندگان و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات درودگری (به‌جز اره‌کشی)</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی انگشتان | درک شفاهی | چابکی دستی | ثبات دست و بازو | مرتب‌سازی اطلاعات | تجسم فضایی | استدلال استقرایی | بیان شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | تشخیص رنگ‌ها | هماهنگی چنداندام | دقت کنترل</t>
+          <t>بینایی نزدیک | مهارت انگشتان | درک شفاهی | مهارت دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | تجسم | استدلال استقرایی | بیان شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | تشخیص گفتار | تشخیص رنگ بصری | هماهنگی چند عضو | دقت کنترل</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کاردان‌های کالیبراسیون تجهیزات | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | تکنسین‌ها و کاردان‌های مهندسی برق و الکترونیک | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکاران تجهیزات برقی و الکترونیکی تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران و تراشکاران | مهندسان مکانیک | مدل‌سازان صنعتی فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندمنظوره | سازندگان و مونتاژکاران قطعات فلزی سازه | مونتاژکاران گروهی و خطوط تولید | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | جوشکاران، برشکاران و لحیم‌کاران | تنظیم‌کنندگان و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان فنی کالیبراسیون | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | مهندسان مکانیک | مدل‌سازان فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | سازندگان و مونتاژکاران سازه‌های فلزی | مونتاژکاران گروهی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
